--- a/artfynd/A 2438-2025 artfynd.xlsx
+++ b/artfynd/A 2438-2025 artfynd.xlsx
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127481338</v>
+        <v>127481246</v>
       </c>
       <c r="B2" t="n">
-        <v>98443</v>
+        <v>78776</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Elakmyrtjärnen, Elakmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>612082</v>
+        <v>612063</v>
       </c>
       <c r="R2" t="n">
-        <v>7061048</v>
+        <v>7061095</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -754,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,45 +782,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127481246</v>
+        <v>127481338</v>
       </c>
       <c r="B3" t="n">
-        <v>78772</v>
+        <v>98447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Elakmyrtjärnen, Elakmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>612063</v>
+        <v>612082</v>
       </c>
       <c r="R3" t="n">
-        <v>7061095</v>
+        <v>7061048</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,42 +898,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127481524</v>
+        <v>127481296</v>
       </c>
       <c r="B4" t="n">
-        <v>98443</v>
+        <v>57661</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -942,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>612095</v>
+        <v>612077</v>
       </c>
       <c r="R4" t="n">
-        <v>7061127</v>
+        <v>7061059</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -977,7 +973,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +983,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,38 +1015,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127481296</v>
+        <v>127481524</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>98447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1054,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>612077</v>
+        <v>612095</v>
       </c>
       <c r="R5" t="n">
-        <v>7061059</v>
+        <v>7061127</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1089,7 +1094,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,12 +1104,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,7 +1134,7 @@
         <v>127481384</v>
       </c>
       <c r="B6" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>127481252</v>
       </c>
       <c r="B7" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>127481230</v>
       </c>
       <c r="B8" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 2438-2025 artfynd.xlsx
+++ b/artfynd/A 2438-2025 artfynd.xlsx
@@ -898,38 +898,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127481296</v>
+        <v>127481524</v>
       </c>
       <c r="B4" t="n">
-        <v>57661</v>
+        <v>98447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -938,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>612077</v>
+        <v>612095</v>
       </c>
       <c r="R4" t="n">
-        <v>7061059</v>
+        <v>7061127</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -973,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -983,12 +987,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:07</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,42 +1014,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127481524</v>
+        <v>127481296</v>
       </c>
       <c r="B5" t="n">
-        <v>98447</v>
+        <v>57661</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1059,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>612095</v>
+        <v>612077</v>
       </c>
       <c r="R5" t="n">
-        <v>7061127</v>
+        <v>7061059</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1094,7 +1089,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1104,7 +1099,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 2438-2025 artfynd.xlsx
+++ b/artfynd/A 2438-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>127481338</v>
       </c>
       <c r="B3" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,42 +898,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127481524</v>
+        <v>127481296</v>
       </c>
       <c r="B4" t="n">
-        <v>98447</v>
+        <v>57661</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -942,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>612095</v>
+        <v>612077</v>
       </c>
       <c r="R4" t="n">
-        <v>7061127</v>
+        <v>7061059</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -977,7 +973,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +983,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,38 +1015,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127481296</v>
+        <v>127481524</v>
       </c>
       <c r="B5" t="n">
-        <v>57661</v>
+        <v>98448</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1054,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>612077</v>
+        <v>612095</v>
       </c>
       <c r="R5" t="n">
-        <v>7061059</v>
+        <v>7061127</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1089,7 +1094,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,12 +1104,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,7 +1134,7 @@
         <v>127481384</v>
       </c>
       <c r="B6" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 2438-2025 artfynd.xlsx
+++ b/artfynd/A 2438-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127481246</v>
       </c>
       <c r="B2" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127481338</v>
       </c>
       <c r="B3" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>127481296</v>
       </c>
       <c r="B4" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>127481524</v>
       </c>
       <c r="B5" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>127481384</v>
       </c>
       <c r="B6" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>127481252</v>
       </c>
       <c r="B7" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>127481230</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 2438-2025 artfynd.xlsx
+++ b/artfynd/A 2438-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>127481338</v>
       </c>
       <c r="B3" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>127481524</v>
       </c>
       <c r="B5" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>127481384</v>
       </c>
       <c r="B6" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 2438-2025 artfynd.xlsx
+++ b/artfynd/A 2438-2025 artfynd.xlsx
@@ -675,45 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127481246</v>
+        <v>127481338</v>
       </c>
       <c r="B2" t="n">
-        <v>78778</v>
+        <v>98459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Elakmyrtjärnen, Elakmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>612063</v>
+        <v>612082</v>
       </c>
       <c r="R2" t="n">
-        <v>7061095</v>
+        <v>7061048</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -745,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,54 +791,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127481338</v>
+        <v>127481246</v>
       </c>
       <c r="B3" t="n">
-        <v>98456</v>
+        <v>78781</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Elakmyrtjärnen, Elakmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>612082</v>
+        <v>612063</v>
       </c>
       <c r="R3" t="n">
-        <v>7061048</v>
+        <v>7061095</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,7 +901,7 @@
         <v>127481296</v>
       </c>
       <c r="B4" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>127481524</v>
       </c>
       <c r="B5" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>127481384</v>
       </c>
       <c r="B6" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>127481252</v>
       </c>
       <c r="B7" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>127481230</v>
       </c>
       <c r="B8" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 2438-2025 artfynd.xlsx
+++ b/artfynd/A 2438-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127481338</v>
       </c>
       <c r="B2" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127481246</v>
       </c>
       <c r="B3" t="n">
-        <v>78781</v>
+        <v>78787</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>127481296</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>127481524</v>
       </c>
       <c r="B5" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>127481384</v>
       </c>
       <c r="B6" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>127481252</v>
       </c>
       <c r="B7" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>127481230</v>
       </c>
       <c r="B8" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 2438-2025 artfynd.xlsx
+++ b/artfynd/A 2438-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127481338</v>
       </c>
       <c r="B2" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -898,38 +898,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127481296</v>
+        <v>127481524</v>
       </c>
       <c r="B4" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -938,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>612077</v>
+        <v>612095</v>
       </c>
       <c r="R4" t="n">
-        <v>7061059</v>
+        <v>7061127</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -973,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -983,12 +987,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:07</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,42 +1014,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127481524</v>
+        <v>127481296</v>
       </c>
       <c r="B5" t="n">
-        <v>98467</v>
+        <v>57672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1059,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>612095</v>
+        <v>612077</v>
       </c>
       <c r="R5" t="n">
-        <v>7061127</v>
+        <v>7061059</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1094,7 +1089,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1104,7 +1099,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,7 +1134,7 @@
         <v>127481384</v>
       </c>
       <c r="B6" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 2438-2025 artfynd.xlsx
+++ b/artfynd/A 2438-2025 artfynd.xlsx
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127481338</v>
+        <v>127481246</v>
       </c>
       <c r="B2" t="n">
-        <v>98468</v>
+        <v>78787</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Elakmyrtjärnen, Elakmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>612082</v>
+        <v>612063</v>
       </c>
       <c r="R2" t="n">
-        <v>7061048</v>
+        <v>7061095</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -754,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,45 +782,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127481246</v>
+        <v>127481338</v>
       </c>
       <c r="B3" t="n">
-        <v>78787</v>
+        <v>98468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Elakmyrtjärnen, Elakmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>612063</v>
+        <v>612082</v>
       </c>
       <c r="R3" t="n">
-        <v>7061095</v>
+        <v>7061048</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 2438-2025 artfynd.xlsx
+++ b/artfynd/A 2438-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>127481338</v>
       </c>
       <c r="B3" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,42 +898,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127481524</v>
+        <v>127481296</v>
       </c>
       <c r="B4" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -942,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>612095</v>
+        <v>612077</v>
       </c>
       <c r="R4" t="n">
-        <v>7061127</v>
+        <v>7061059</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -977,7 +973,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +983,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,38 +1015,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127481296</v>
+        <v>127481524</v>
       </c>
       <c r="B5" t="n">
-        <v>57672</v>
+        <v>98469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1054,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>612077</v>
+        <v>612095</v>
       </c>
       <c r="R5" t="n">
-        <v>7061059</v>
+        <v>7061127</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1089,7 +1094,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,12 +1104,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,7 +1134,7 @@
         <v>127481384</v>
       </c>
       <c r="B6" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 2438-2025 artfynd.xlsx
+++ b/artfynd/A 2438-2025 artfynd.xlsx
@@ -675,45 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127481246</v>
+        <v>127481338</v>
       </c>
       <c r="B2" t="n">
-        <v>78787</v>
+        <v>98470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Elakmyrtjärnen, Elakmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>612063</v>
+        <v>612082</v>
       </c>
       <c r="R2" t="n">
-        <v>7061095</v>
+        <v>7061048</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -745,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,54 +791,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127481338</v>
+        <v>127481246</v>
       </c>
       <c r="B3" t="n">
-        <v>98469</v>
+        <v>78787</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Elakmyrtjärnen, Elakmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>612082</v>
+        <v>612063</v>
       </c>
       <c r="R3" t="n">
-        <v>7061048</v>
+        <v>7061095</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1018,7 +1018,7 @@
         <v>127481524</v>
       </c>
       <c r="B5" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>127481384</v>
       </c>
       <c r="B6" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 2438-2025 artfynd.xlsx
+++ b/artfynd/A 2438-2025 artfynd.xlsx
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127481338</v>
+        <v>127481246</v>
       </c>
       <c r="B2" t="n">
-        <v>98470</v>
+        <v>78787</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Elakmyrtjärnen, Elakmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>612082</v>
+        <v>612063</v>
       </c>
       <c r="R2" t="n">
-        <v>7061048</v>
+        <v>7061095</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -754,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,45 +782,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127481246</v>
+        <v>127481338</v>
       </c>
       <c r="B3" t="n">
-        <v>78787</v>
+        <v>98470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Elakmyrtjärnen, Elakmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>612063</v>
+        <v>612082</v>
       </c>
       <c r="R3" t="n">
-        <v>7061095</v>
+        <v>7061048</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
